--- a/65_Threshold_OUTPUT/direct_Q7CFV3_Yersinia_pestis_biovar_Microtus_str__91001.xlsx
+++ b/65_Threshold_OUTPUT/direct_Q7CFV3_Yersinia_pestis_biovar_Microtus_str__91001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,15 +446,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>full_pattern</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>group1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>group2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>full_pattern_html</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
@@ -477,15 +487,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>GATTGAT</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>GAT</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>GAT</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;T&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0.9960015993602559</v>
       </c>
     </row>
@@ -506,15 +526,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>GTTAGATTGATCACGTT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>GTT</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>GTT</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;AGATTGATCAC&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>0.9960015993602559</v>
       </c>
     </row>
@@ -535,15 +565,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>GCAAGGTGTTAGATTGATCACGTTTCCAGCA</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>GCA</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>GCA</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;AGGTGTTAGATTGATCACGTTTCCA&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>0.9960015993602559</v>
       </c>
     </row>
@@ -564,15 +604,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>GGCAAGG</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>GG</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>GG</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;CAA&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -593,15 +643,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>GTGT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -622,15 +682,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>AGGTGTTAG</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>AG</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>AG</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;GTGTT&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -651,15 +721,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>TTAGATT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;AGA&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -680,15 +760,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>TGTTAGATTG</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>TG</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>TG</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;TTAGAT&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -709,15 +799,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>CAAGGTGTTAGATTGATCA</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;AGGTGTTAGATTGAT&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -738,15 +838,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>GTGTTAGATTGATCACGT</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;GTTAGATTGATCAC&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -767,15 +877,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>TTGATCACGTT</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;GATCACG&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -796,15 +916,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>TTAGATTGATCACGTTT</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;AGATTGATCACGT&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -825,15 +955,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>TTGATCACGTTT</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;GATCACGT&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -854,15 +994,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>TTT</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: purple; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -883,15 +1033,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>TCACGTTTC</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>TC</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>TC</t>
         </is>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;ACGTT&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -912,15 +1072,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>CAAGGTGTTAGATTGATCACGTTTCCA</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;AGGTGTTAGATTGATCACGTTTC&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -941,15 +1111,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>CACGTTTCCA</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;CGTTTC&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -970,15 +1150,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>AGGTGTTAGATTGATCACGTTTCCAG</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>AG</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>AG</t>
         </is>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;GTGTTAGATTGATCACGTTTCC&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -999,15 +1189,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>AGATTGATCACGTTTCCAG</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>AG</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>AG</t>
         </is>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;ATTGATCACGTTTCC&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -1028,15 +1228,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>CACGTTTCCAGCA</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;CGTTTCCAG&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -1057,15 +1267,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>CAGCA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;G&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
